--- a/tests/fixtures/catalog-import/with-errors.xlsx
+++ b/tests/fixtures/catalog-import/with-errors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>sku</t>
   </si>
@@ -25,15 +25,6 @@
     <t>unit</t>
   </si>
   <si>
-    <t>unit_price</t>
-  </si>
-  <si>
-    <t>on_hand</t>
-  </si>
-  <si>
-    <t>stock_state</t>
-  </si>
-  <si>
     <t>vendor_code</t>
   </si>
   <si>
@@ -55,31 +46,19 @@
     <t>pcs</t>
   </si>
   <si>
-    <t>in-stock</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>missing sku</t>
   </si>
   <si>
-    <t>FX-BAD</t>
-  </si>
-  <si>
-    <t>bad price</t>
-  </si>
-  <si>
-    <t>$1.0</t>
-  </si>
-  <si>
-    <t>FX-BAD2</t>
-  </si>
-  <si>
-    <t>bad enum</t>
-  </si>
-  <si>
-    <t>weird</t>
+    <t>FX-DUP</t>
+  </si>
+  <si>
+    <t>dup row</t>
+  </si>
+  <si>
+    <t>dup again</t>
   </si>
   <si>
     <t>FX-BAD3</t>
@@ -465,10 +444,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -490,174 +469,120 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
